--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/203.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/203.xlsx
@@ -426,13 +426,13 @@
         <v>-13.0895250940898</v>
       </c>
       <c r="E2">
-        <v>-14.80137371246626</v>
+        <v>-15.89109211225003</v>
       </c>
       <c r="F2">
-        <v>3.52241549570743</v>
+        <v>0.4075621130442239</v>
       </c>
       <c r="G2">
-        <v>-6.188370821772571</v>
+        <v>-7.180266544612387</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.82494704318565</v>
       </c>
       <c r="E3">
-        <v>-14.63536438381907</v>
+        <v>-15.97180763296275</v>
       </c>
       <c r="F3">
-        <v>3.40412058235368</v>
+        <v>0.9863211050179082</v>
       </c>
       <c r="G3">
-        <v>-6.648225460450575</v>
+        <v>-4.573046405159363</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.49172824971662</v>
       </c>
       <c r="E4">
-        <v>-14.70751656018328</v>
+        <v>-17.31715839047951</v>
       </c>
       <c r="F4">
-        <v>3.683199655066504</v>
+        <v>1.092177592111796</v>
       </c>
       <c r="G4">
-        <v>-5.578081683244545</v>
+        <v>-6.489984694218951</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.10128062376359</v>
       </c>
       <c r="E5">
-        <v>-15.68155961991512</v>
+        <v>-18.90927475362225</v>
       </c>
       <c r="F5">
-        <v>4.058721666911844</v>
+        <v>1.283634967641102</v>
       </c>
       <c r="G5">
-        <v>-6.034447006924157</v>
+        <v>-5.581829220795001</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.64879741293377</v>
       </c>
       <c r="E6">
-        <v>-17.08837535513799</v>
+        <v>-17.58605012010696</v>
       </c>
       <c r="F6">
-        <v>3.835449223247275</v>
+        <v>1.53469194788614</v>
       </c>
       <c r="G6">
-        <v>-5.840531801961347</v>
+        <v>-6.270233991867669</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.14399295942204</v>
       </c>
       <c r="E7">
-        <v>-16.63141157149799</v>
+        <v>-17.41764522870971</v>
       </c>
       <c r="F7">
-        <v>3.909322769378864</v>
+        <v>1.221157769277016</v>
       </c>
       <c r="G7">
-        <v>-6.398954623525611</v>
+        <v>-3.491977827673739</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.59836107920824</v>
       </c>
       <c r="E8">
-        <v>-17.25845578191808</v>
+        <v>-20.0649322634317</v>
       </c>
       <c r="F8">
-        <v>3.96893504374192</v>
+        <v>2.070454907961559</v>
       </c>
       <c r="G8">
-        <v>-5.770421068530663</v>
+        <v>-6.759866987671417</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.02304187995991</v>
       </c>
       <c r="E9">
-        <v>-19.12258852175356</v>
+        <v>-19.22839631694277</v>
       </c>
       <c r="F9">
-        <v>3.812217841173694</v>
+        <v>1.460026548796832</v>
       </c>
       <c r="G9">
-        <v>-5.43570505123711</v>
+        <v>-6.251873706306871</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.429711560456886</v>
       </c>
       <c r="E10">
-        <v>-18.11465436254831</v>
+        <v>-21.58697049130574</v>
       </c>
       <c r="F10">
-        <v>4.273741419051058</v>
+        <v>1.08925248728598</v>
       </c>
       <c r="G10">
-        <v>-4.834827793677232</v>
+        <v>-3.561777369823733</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.832855351922404</v>
       </c>
       <c r="E11">
-        <v>-18.32108937866197</v>
+        <v>-20.11290238859496</v>
       </c>
       <c r="F11">
-        <v>4.286167175663596</v>
+        <v>2.139990683590759</v>
       </c>
       <c r="G11">
-        <v>-3.137732902244026</v>
+        <v>-3.118230478472179</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.246268127503386</v>
       </c>
       <c r="E12">
-        <v>-18.82693803921478</v>
+        <v>-22.08437807630825</v>
       </c>
       <c r="F12">
-        <v>4.578870870366946</v>
+        <v>2.261007987413149</v>
       </c>
       <c r="G12">
-        <v>-2.827624169943876</v>
+        <v>-4.379247069290428</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.685965587862983</v>
       </c>
       <c r="E13">
-        <v>-21.45463489537959</v>
+        <v>-22.52493972709248</v>
       </c>
       <c r="F13">
-        <v>4.287990021172266</v>
+        <v>1.550269279270403</v>
       </c>
       <c r="G13">
-        <v>-2.917618039883424</v>
+        <v>-4.286816637833976</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.177315441909211</v>
       </c>
       <c r="E14">
-        <v>-21.02097463898306</v>
+        <v>-23.67703785633191</v>
       </c>
       <c r="F14">
-        <v>4.496279023170863</v>
+        <v>2.753404328406089</v>
       </c>
       <c r="G14">
-        <v>-2.971877881272079</v>
+        <v>-2.83782396075037</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.736772973222386</v>
       </c>
       <c r="E15">
-        <v>-21.46423978874986</v>
+        <v>-25.19744583356319</v>
       </c>
       <c r="F15">
-        <v>5.06275795947623</v>
+        <v>2.074125938273548</v>
       </c>
       <c r="G15">
-        <v>-1.828183713820062</v>
+        <v>-1.895152739533978</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.37663793730807</v>
       </c>
       <c r="E16">
-        <v>-25.14315848715924</v>
+        <v>-25.93206394403549</v>
       </c>
       <c r="F16">
-        <v>5.497939756862089</v>
+        <v>3.230169492013642</v>
       </c>
       <c r="G16">
-        <v>-2.144983058655078</v>
+        <v>-2.406473119165492</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.103925237263355</v>
       </c>
       <c r="E17">
-        <v>-23.44243573189054</v>
+        <v>-26.57310566761329</v>
       </c>
       <c r="F17">
-        <v>5.241624872977792</v>
+        <v>2.708398573701131</v>
       </c>
       <c r="G17">
-        <v>-0.2005672416195395</v>
+        <v>-2.339444503631868</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.918037450820138</v>
       </c>
       <c r="E18">
-        <v>-24.38765505456356</v>
+        <v>-24.93266142986069</v>
       </c>
       <c r="F18">
-        <v>5.750160760954976</v>
+        <v>3.144953444115676</v>
       </c>
       <c r="G18">
-        <v>-0.5226237327709191</v>
+        <v>-2.041121313451523</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.814740580941396</v>
       </c>
       <c r="E19">
-        <v>-25.90648712284017</v>
+        <v>-27.10976153684028</v>
       </c>
       <c r="F19">
-        <v>5.73718545838978</v>
+        <v>2.822751643031352</v>
       </c>
       <c r="G19">
-        <v>-0.007721342865914322</v>
+        <v>-2.896089562241543</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.793007975637163</v>
       </c>
       <c r="E20">
-        <v>-26.69647488500425</v>
+        <v>-28.74373458523592</v>
       </c>
       <c r="F20">
-        <v>5.937069733095139</v>
+        <v>3.918378399803347</v>
       </c>
       <c r="G20">
-        <v>0.3920799997297099</v>
+        <v>-1.51953493210273</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.846955613494926</v>
       </c>
       <c r="E21">
-        <v>-27.20268129500367</v>
+        <v>-27.75273691881936</v>
       </c>
       <c r="F21">
-        <v>6.034768551018598</v>
+        <v>3.860706165186704</v>
       </c>
       <c r="G21">
-        <v>0.6264765555467278</v>
+        <v>0.05831079846038877</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.967254741280712</v>
       </c>
       <c r="E22">
-        <v>-27.40156734494654</v>
+        <v>-29.66021394761925</v>
       </c>
       <c r="F22">
-        <v>5.972422800245494</v>
+        <v>3.84959488448398</v>
       </c>
       <c r="G22">
-        <v>0.6398809544352367</v>
+        <v>-1.430689821465309</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.143673727664053</v>
       </c>
       <c r="E23">
-        <v>-27.0103524754239</v>
+        <v>-27.1179218470021</v>
       </c>
       <c r="F23">
-        <v>6.449232307618679</v>
+        <v>3.922451691417857</v>
       </c>
       <c r="G23">
-        <v>0.1297027130147719</v>
+        <v>0.05332842742378564</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.362981548947709</v>
       </c>
       <c r="E24">
-        <v>-28.93440598332888</v>
+        <v>-30.71391512938302</v>
       </c>
       <c r="F24">
-        <v>6.437078948423597</v>
+        <v>3.547778545943193</v>
       </c>
       <c r="G24">
-        <v>0.8783825867209508</v>
+        <v>1.586511588116597</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.611366049871949</v>
       </c>
       <c r="E25">
-        <v>-29.12101534023695</v>
+        <v>-30.80517293758559</v>
       </c>
       <c r="F25">
-        <v>6.381636571735893</v>
+        <v>4.41287790225199</v>
       </c>
       <c r="G25">
-        <v>1.084272034899304</v>
+        <v>-2.66417260503344</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.880267875003701</v>
       </c>
       <c r="E26">
-        <v>-29.41165733052325</v>
+        <v>-32.32079884626477</v>
       </c>
       <c r="F26">
-        <v>6.30650397940153</v>
+        <v>4.520889813096792</v>
       </c>
       <c r="G26">
-        <v>1.143563905507651</v>
+        <v>0.2978817369552875</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.161510390050148</v>
       </c>
       <c r="E27">
-        <v>-30.41845937122658</v>
+        <v>-30.08781510579353</v>
       </c>
       <c r="F27">
-        <v>6.481964341478982</v>
+        <v>3.800450906221979</v>
       </c>
       <c r="G27">
-        <v>2.190785465399767</v>
+        <v>0.3126202856961228</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.44515588947723</v>
       </c>
       <c r="E28">
-        <v>-30.58976927869974</v>
+        <v>-31.70607887785655</v>
       </c>
       <c r="F28">
-        <v>5.987021401374014</v>
+        <v>4.166179280686242</v>
       </c>
       <c r="G28">
-        <v>0.7386808755092461</v>
+        <v>0.0487598745795914</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.721587013813815</v>
       </c>
       <c r="E29">
-        <v>-29.95347566011898</v>
+        <v>-29.47205811683756</v>
       </c>
       <c r="F29">
-        <v>6.315949201481211</v>
+        <v>3.945982393909456</v>
       </c>
       <c r="G29">
-        <v>0.3973901147747008</v>
+        <v>-0.790652120721393</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.980771071309544</v>
       </c>
       <c r="E30">
-        <v>-29.18802317012845</v>
+        <v>-31.890544002322</v>
       </c>
       <c r="F30">
-        <v>6.020554790427529</v>
+        <v>3.427020969890934</v>
       </c>
       <c r="G30">
-        <v>0.7598021560497962</v>
+        <v>-2.423489323237346</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.210423751183454</v>
       </c>
       <c r="E31">
-        <v>-28.70886986385086</v>
+        <v>-30.89690849979597</v>
       </c>
       <c r="F31">
-        <v>6.136863736563318</v>
+        <v>3.579558772548316</v>
       </c>
       <c r="G31">
-        <v>1.044542177882511</v>
+        <v>-1.251847530342801</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.405000267574009</v>
       </c>
       <c r="E32">
-        <v>-29.1185609073248</v>
+        <v>-29.70225403606946</v>
       </c>
       <c r="F32">
-        <v>5.686668407099092</v>
+        <v>4.153251489298509</v>
       </c>
       <c r="G32">
-        <v>-0.3925226036231008</v>
+        <v>-1.14201687153194</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.562864298874173</v>
       </c>
       <c r="E33">
-        <v>-28.93911559629685</v>
+        <v>-28.18966220497542</v>
       </c>
       <c r="F33">
-        <v>6.259038729409895</v>
+        <v>3.804129855063545</v>
       </c>
       <c r="G33">
-        <v>0.9218963972891313</v>
+        <v>-1.894288687148229</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.681441172046206</v>
       </c>
       <c r="E34">
-        <v>-29.65098718182863</v>
+        <v>-28.32493678053255</v>
       </c>
       <c r="F34">
-        <v>6.796711638819333</v>
+        <v>4.036373992739078</v>
       </c>
       <c r="G34">
-        <v>0.8351104459771372</v>
+        <v>-1.532959194264475</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.759608847310579</v>
       </c>
       <c r="E35">
-        <v>-28.52135934061526</v>
+        <v>-31.13049851029663</v>
       </c>
       <c r="F35">
-        <v>6.792958255799741</v>
+        <v>4.489467504028558</v>
       </c>
       <c r="G35">
-        <v>0.8289627629107106</v>
+        <v>-0.9560569074999993</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.797325370753631</v>
       </c>
       <c r="E36">
-        <v>-28.138639888331</v>
+        <v>-30.63116632384086</v>
       </c>
       <c r="F36">
-        <v>6.254401638489488</v>
+        <v>4.343552759509544</v>
       </c>
       <c r="G36">
-        <v>-0.3492405312426692</v>
+        <v>-1.982001591211219</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.792911063858611</v>
       </c>
       <c r="E37">
-        <v>-26.19404522232724</v>
+        <v>-26.03145036308183</v>
       </c>
       <c r="F37">
-        <v>6.538353774304118</v>
+        <v>3.47834096008075</v>
       </c>
       <c r="G37">
-        <v>-0.1747449864132243</v>
+        <v>-0.5266923932386834</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.747647765886279</v>
       </c>
       <c r="E38">
-        <v>-26.28484565465503</v>
+        <v>-29.08825635926547</v>
       </c>
       <c r="F38">
-        <v>6.383888601547648</v>
+        <v>4.016148484493001</v>
       </c>
       <c r="G38">
-        <v>-0.109785461841645</v>
+        <v>-1.560029525139095</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.66745152025242</v>
       </c>
       <c r="E39">
-        <v>-24.65904650184325</v>
+        <v>-26.51312150090769</v>
       </c>
       <c r="F39">
-        <v>6.519016725076603</v>
+        <v>4.134720546381953</v>
       </c>
       <c r="G39">
-        <v>-0.005142427890822067</v>
+        <v>-1.501300447272425</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.55632113857251</v>
       </c>
       <c r="E40">
-        <v>-24.52445572586127</v>
+        <v>-26.14983373059035</v>
       </c>
       <c r="F40">
-        <v>6.466711669807385</v>
+        <v>4.910513142413205</v>
       </c>
       <c r="G40">
-        <v>-0.6399163612272973</v>
+        <v>-1.144175347223545</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.417223409574378</v>
       </c>
       <c r="E41">
-        <v>-25.1586639821615</v>
+        <v>-26.17036583174113</v>
       </c>
       <c r="F41">
-        <v>6.870805320073168</v>
+        <v>4.296513526409162</v>
       </c>
       <c r="G41">
-        <v>-1.558592748375052</v>
+        <v>-2.306997846801471</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.253285206426954</v>
       </c>
       <c r="E42">
-        <v>-25.29224490843976</v>
+        <v>-22.90437603572117</v>
       </c>
       <c r="F42">
-        <v>6.758710615378363</v>
+        <v>4.121293887630856</v>
       </c>
       <c r="G42">
-        <v>0.0356269404253026</v>
+        <v>-1.604056470265863</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.06593917604935</v>
       </c>
       <c r="E43">
-        <v>-23.2233209885554</v>
+        <v>-24.21645156622958</v>
       </c>
       <c r="F43">
-        <v>7.370871548814581</v>
+        <v>4.818704126789265</v>
       </c>
       <c r="G43">
-        <v>-1.591026163023292</v>
+        <v>-1.042104607156736</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.856455737473066</v>
       </c>
       <c r="E44">
-        <v>-21.40063284283812</v>
+        <v>-23.41864765792825</v>
       </c>
       <c r="F44">
-        <v>7.019828879304189</v>
+        <v>4.024399592312441</v>
       </c>
       <c r="G44">
-        <v>-0.8054469487363959</v>
+        <v>-3.125897701941131</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.630592576235848</v>
       </c>
       <c r="E45">
-        <v>-21.21506503495181</v>
+        <v>-21.52966718121268</v>
       </c>
       <c r="F45">
-        <v>7.531022225807479</v>
+        <v>4.114791191142062</v>
       </c>
       <c r="G45">
-        <v>-1.494480723461526</v>
+        <v>-1.531204605128661</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.395212721617209</v>
       </c>
       <c r="E46">
-        <v>-19.81196264841522</v>
+        <v>-20.12462207932681</v>
       </c>
       <c r="F46">
-        <v>7.140217451878149</v>
+        <v>3.900379582074377</v>
       </c>
       <c r="G46">
-        <v>-2.047331896883196</v>
+        <v>-2.437830606513468</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.154685411282194</v>
       </c>
       <c r="E47">
-        <v>-19.83762098214268</v>
+        <v>-21.76184657205995</v>
       </c>
       <c r="F47">
-        <v>7.460846632988442</v>
+        <v>4.382237943905984</v>
       </c>
       <c r="G47">
-        <v>-1.169206382045975</v>
+        <v>-3.367802575041216</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.913457455375223</v>
       </c>
       <c r="E48">
-        <v>-19.53355206642365</v>
+        <v>-18.59354954580747</v>
       </c>
       <c r="F48">
-        <v>7.334161245694695</v>
+        <v>4.909276268093246</v>
       </c>
       <c r="G48">
-        <v>-1.670515671966732</v>
+        <v>-2.39675997855327</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.675142662038721</v>
       </c>
       <c r="E49">
-        <v>-19.01830682230493</v>
+        <v>-20.34640409385246</v>
       </c>
       <c r="F49">
-        <v>7.000113324362883</v>
+        <v>4.74257221602226</v>
       </c>
       <c r="G49">
-        <v>-1.233351512414893</v>
+        <v>-0.7698983107357019</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.441546207607582</v>
       </c>
       <c r="E50">
-        <v>-17.21195741080732</v>
+        <v>-19.48011607313314</v>
       </c>
       <c r="F50">
-        <v>7.267914827251863</v>
+        <v>4.816806847102568</v>
       </c>
       <c r="G50">
-        <v>-1.863335086356043</v>
+        <v>-2.525232319295767</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.216302979747824</v>
       </c>
       <c r="E51">
-        <v>-18.4233604356512</v>
+        <v>-18.84281486908568</v>
       </c>
       <c r="F51">
-        <v>6.939799468279287</v>
+        <v>5.068258170120551</v>
       </c>
       <c r="G51">
-        <v>-2.022671643161165</v>
+        <v>-2.913946644880372</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.007751109102255</v>
       </c>
       <c r="E52">
-        <v>-17.44847960822794</v>
+        <v>-16.53094737563782</v>
       </c>
       <c r="F52">
-        <v>7.068564261440007</v>
+        <v>5.153478969136263</v>
       </c>
       <c r="G52">
-        <v>-1.567352451871963</v>
+        <v>-2.848027062102404</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.819848713301344</v>
       </c>
       <c r="E53">
-        <v>-16.5070868460914</v>
+        <v>-17.31125778884751</v>
       </c>
       <c r="F53">
-        <v>7.505282253563842</v>
+        <v>4.861063508909523</v>
       </c>
       <c r="G53">
-        <v>-1.910848035935663</v>
+        <v>0.05687071115080581</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.656065753831834</v>
       </c>
       <c r="E54">
-        <v>-16.52333048235692</v>
+        <v>-16.32279606787525</v>
       </c>
       <c r="F54">
-        <v>7.4131755012278</v>
+        <v>4.867344486570156</v>
       </c>
       <c r="G54">
-        <v>-1.543622461446467</v>
+        <v>-1.293494193226833</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.519346148089354</v>
       </c>
       <c r="E55">
-        <v>-14.75132954620749</v>
+        <v>-17.4535333852205</v>
       </c>
       <c r="F55">
-        <v>7.3905269229311</v>
+        <v>4.427212024492633</v>
       </c>
       <c r="G55">
-        <v>-2.417348261261997</v>
+        <v>-2.016626587006456</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.409058759133814</v>
       </c>
       <c r="E56">
-        <v>-13.14724442626248</v>
+        <v>-14.65174840277882</v>
       </c>
       <c r="F56">
-        <v>7.520317957525024</v>
+        <v>4.772089326874219</v>
       </c>
       <c r="G56">
-        <v>-2.21188587345821</v>
+        <v>-1.455230895547927</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.325273731620872</v>
       </c>
       <c r="E57">
-        <v>-14.50680553521532</v>
+        <v>-14.27689038137189</v>
       </c>
       <c r="F57">
-        <v>7.1663485994829</v>
+        <v>5.138918376949713</v>
       </c>
       <c r="G57">
-        <v>-2.576959593346879</v>
+        <v>-1.515078937806871</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.271431743345071</v>
       </c>
       <c r="E58">
-        <v>-12.95355253600641</v>
+        <v>-17.2297769560275</v>
       </c>
       <c r="F58">
-        <v>7.398483461450268</v>
+        <v>5.022123233097885</v>
       </c>
       <c r="G58">
-        <v>-2.532363234387357</v>
+        <v>-1.380233796901277</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.246988913410641</v>
       </c>
       <c r="E59">
-        <v>-13.72732836122303</v>
+        <v>-14.14037500393665</v>
       </c>
       <c r="F59">
-        <v>7.304018571006136</v>
+        <v>4.446724865076763</v>
       </c>
       <c r="G59">
-        <v>-3.602775165782067</v>
+        <v>-2.511284990938818</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.249713683893111</v>
       </c>
       <c r="E60">
-        <v>-12.69686051535562</v>
+        <v>-12.66102670053292</v>
       </c>
       <c r="F60">
-        <v>7.080389793510593</v>
+        <v>5.043542855604203</v>
       </c>
       <c r="G60">
-        <v>-1.860120546637411</v>
+        <v>-2.081877439585491</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.276504748852897</v>
       </c>
       <c r="E61">
-        <v>-13.59657773119957</v>
+        <v>-14.27931764344</v>
       </c>
       <c r="F61">
-        <v>7.559128254688783</v>
+        <v>3.997809169992212</v>
       </c>
       <c r="G61">
-        <v>-2.448851412613702</v>
+        <v>-3.787940598884583</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.322052920661259</v>
       </c>
       <c r="E62">
-        <v>-13.25148084097104</v>
+        <v>-12.33531167905723</v>
       </c>
       <c r="F62">
-        <v>7.427181796343946</v>
+        <v>5.028415296699925</v>
       </c>
       <c r="G62">
-        <v>-2.761628444618505</v>
+        <v>-1.828998108022722</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.380866738713738</v>
       </c>
       <c r="E63">
-        <v>-12.70463137675278</v>
+        <v>-12.6778952662115</v>
       </c>
       <c r="F63">
-        <v>7.168570538882261</v>
+        <v>4.409906869954626</v>
       </c>
       <c r="G63">
-        <v>-2.967680109528283</v>
+        <v>-3.736405336474748</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.450861380798596</v>
       </c>
       <c r="E64">
-        <v>-10.26555451995546</v>
+        <v>-10.57634369110188</v>
       </c>
       <c r="F64">
-        <v>7.443506636920296</v>
+        <v>4.143019165378855</v>
       </c>
       <c r="G64">
-        <v>-2.623591937813053</v>
+        <v>-3.003837887908202</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.529379219735121</v>
       </c>
       <c r="E65">
-        <v>-9.970221030597221</v>
+        <v>-12.48915752651981</v>
       </c>
       <c r="F65">
-        <v>6.925913534812714</v>
+        <v>5.204933574328891</v>
       </c>
       <c r="G65">
-        <v>-1.934654168908562</v>
+        <v>-1.861798993225821</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.612205799202072</v>
       </c>
       <c r="E66">
-        <v>-10.82578109639237</v>
+        <v>-13.1984976950813</v>
       </c>
       <c r="F66">
-        <v>6.602180290108159</v>
+        <v>4.37766578492811</v>
       </c>
       <c r="G66">
-        <v>-2.798650275384174</v>
+        <v>-2.404314643473887</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.695339722875095</v>
       </c>
       <c r="E67">
-        <v>-11.61229099051857</v>
+        <v>-10.10111204331493</v>
       </c>
       <c r="F67">
-        <v>6.975447104729914</v>
+        <v>3.899185467814136</v>
       </c>
       <c r="G67">
-        <v>-2.143072873878919</v>
+        <v>-3.779419254666499</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.774553899388524</v>
       </c>
       <c r="E68">
-        <v>-9.539060491852918</v>
+        <v>-10.50072270364779</v>
       </c>
       <c r="F68">
-        <v>6.273578733419543</v>
+        <v>3.11189991795454</v>
       </c>
       <c r="G68">
-        <v>-2.38331254257275</v>
+        <v>-2.959473267136429</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.844844369261658</v>
       </c>
       <c r="E69">
-        <v>-10.6783747389687</v>
+        <v>-11.45816437766751</v>
       </c>
       <c r="F69">
-        <v>6.673367871007162</v>
+        <v>3.323699995967665</v>
       </c>
       <c r="G69">
-        <v>-2.643759781238293</v>
+        <v>-3.530942948670961</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.905222340073093</v>
       </c>
       <c r="E70">
-        <v>-10.10312721424834</v>
+        <v>-9.878170739443306</v>
       </c>
       <c r="F70">
-        <v>6.108249338083158</v>
+        <v>3.424472787072993</v>
       </c>
       <c r="G70">
-        <v>-2.275547664178395</v>
+        <v>-2.965134300008583</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.95722490881418</v>
       </c>
       <c r="E71">
-        <v>-9.522522504776907</v>
+        <v>-11.54573147955383</v>
       </c>
       <c r="F71">
-        <v>5.593776136628992</v>
+        <v>3.867104337085079</v>
       </c>
       <c r="G71">
-        <v>-2.403357895813038</v>
+        <v>-3.317896101036703</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.000045911476316</v>
       </c>
       <c r="E72">
-        <v>-9.72457848652515</v>
+        <v>-9.306007105522172</v>
       </c>
       <c r="F72">
-        <v>5.79603597020751</v>
+        <v>3.375061162511282</v>
       </c>
       <c r="G72">
-        <v>-2.933419273742365</v>
+        <v>-5.991860149106973</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.033473662611252</v>
       </c>
       <c r="E73">
-        <v>-11.33513026735311</v>
+        <v>-11.2407206412412</v>
       </c>
       <c r="F73">
-        <v>6.258883526230181</v>
+        <v>3.053747820445519</v>
       </c>
       <c r="G73">
-        <v>-2.030706337184976</v>
+        <v>-3.67280644611981</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.057213756425819</v>
       </c>
       <c r="E74">
-        <v>-10.8188887589527</v>
+        <v>-10.75849702958641</v>
       </c>
       <c r="F74">
-        <v>6.001613667678874</v>
+        <v>3.607066160593583</v>
       </c>
       <c r="G74">
-        <v>-2.308404828655661</v>
+        <v>-1.514161916692493</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.068346393953689</v>
       </c>
       <c r="E75">
-        <v>-8.575124986106198</v>
+        <v>-11.39081238375143</v>
       </c>
       <c r="F75">
-        <v>5.635435520734626</v>
+        <v>3.836450125385833</v>
       </c>
       <c r="G75">
-        <v>-2.0350497729325</v>
+        <v>-1.341371302815773</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.066706998566065</v>
       </c>
       <c r="E76">
-        <v>-8.605560859911751</v>
+        <v>-9.897729218682434</v>
       </c>
       <c r="F76">
-        <v>5.454547798484963</v>
+        <v>3.405105647433083</v>
       </c>
       <c r="G76">
-        <v>-1.529559263995643</v>
+        <v>-3.960853702946256</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.055218997785716</v>
       </c>
       <c r="E77">
-        <v>-10.73258510131452</v>
+        <v>-10.57609009655745</v>
       </c>
       <c r="F77">
-        <v>5.266842222269334</v>
+        <v>3.448774754345411</v>
       </c>
       <c r="G77">
-        <v>-1.597425447550703</v>
+        <v>-1.553928189710219</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.034242502297759</v>
       </c>
       <c r="E78">
-        <v>-12.00990459381405</v>
+        <v>-14.32572997354461</v>
       </c>
       <c r="F78">
-        <v>5.563473507642973</v>
+        <v>2.870425942203825</v>
       </c>
       <c r="G78">
-        <v>-1.340821752256254</v>
+        <v>-0.9142149224291508</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.004061615768606</v>
       </c>
       <c r="E79">
-        <v>-10.31743724666134</v>
+        <v>-13.61251343123256</v>
       </c>
       <c r="F79">
-        <v>5.389243685061818</v>
+        <v>3.534190349188722</v>
       </c>
       <c r="G79">
-        <v>-1.447368349892158</v>
+        <v>-1.718707283381903</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.964850659403521</v>
       </c>
       <c r="E80">
-        <v>-11.9588686917476</v>
+        <v>-14.13150372335563</v>
       </c>
       <c r="F80">
-        <v>5.670595375763297</v>
+        <v>2.351540536069245</v>
       </c>
       <c r="G80">
-        <v>-1.285790553756949</v>
+        <v>-2.199044267311377</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.915643292389032</v>
       </c>
       <c r="E81">
-        <v>-14.50310124347704</v>
+        <v>-13.707824223672</v>
       </c>
       <c r="F81">
-        <v>4.253476318157094</v>
+        <v>2.97324171394007</v>
       </c>
       <c r="G81">
-        <v>-0.1881891118482046</v>
+        <v>-2.656329922650906</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.856315693696061</v>
       </c>
       <c r="E82">
-        <v>-12.72474685829485</v>
+        <v>-13.77171193497221</v>
       </c>
       <c r="F82">
-        <v>5.298129916334756</v>
+        <v>2.985330141192619</v>
       </c>
       <c r="G82">
-        <v>-0.4135015307054623</v>
+        <v>-0.30576644722096</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.791340800271869</v>
       </c>
       <c r="E83">
-        <v>-13.17223707431082</v>
+        <v>-14.30617149430548</v>
       </c>
       <c r="F83">
-        <v>4.874450575012733</v>
+        <v>2.975789896758012</v>
       </c>
       <c r="G83">
-        <v>-0.04115785281255331</v>
+        <v>-0.972056774091297</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.725591731865523</v>
       </c>
       <c r="E84">
-        <v>-14.77533498692215</v>
+        <v>-16.32242473300662</v>
       </c>
       <c r="F84">
-        <v>5.255208318614516</v>
+        <v>2.603367197389187</v>
       </c>
       <c r="G84">
-        <v>0.3150104995754766</v>
+        <v>-0.4536418953691254</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.663873983471412</v>
       </c>
       <c r="E85">
-        <v>-15.39687257294892</v>
+        <v>-14.33840517229208</v>
       </c>
       <c r="F85">
-        <v>4.658143269964267</v>
+        <v>2.837855446346898</v>
       </c>
       <c r="G85">
-        <v>0.1890475523517472</v>
+        <v>-2.795889280404422</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.61184858584324</v>
       </c>
       <c r="E86">
-        <v>-16.53314368553154</v>
+        <v>-18.72723915546191</v>
       </c>
       <c r="F86">
-        <v>4.787419600135673</v>
+        <v>2.348396879827098</v>
       </c>
       <c r="G86">
-        <v>1.248336050734506</v>
+        <v>-1.053423362355504</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.575238814305743</v>
       </c>
       <c r="E87">
-        <v>-15.99772408970864</v>
+        <v>-19.75407516517517</v>
       </c>
       <c r="F87">
-        <v>4.633831800456356</v>
+        <v>2.92675044308643</v>
       </c>
       <c r="G87">
-        <v>0.7850980345153674</v>
+        <v>-0.387093308938696</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.558490361416512</v>
       </c>
       <c r="E88">
-        <v>-18.78462850656112</v>
+        <v>-20.57233871904315</v>
       </c>
       <c r="F88">
-        <v>4.710034977989556</v>
+        <v>1.805947513376693</v>
       </c>
       <c r="G88">
-        <v>1.394622437023821</v>
+        <v>0.5504829826927576</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.570446595313229</v>
       </c>
       <c r="E89">
-        <v>-20.92157463451469</v>
+        <v>-22.0925519718921</v>
       </c>
       <c r="F89">
-        <v>3.931090807186579</v>
+        <v>2.130740257338677</v>
       </c>
       <c r="G89">
-        <v>1.334483066757421</v>
+        <v>2.11786407880624</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.620336461145794</v>
       </c>
       <c r="E90">
-        <v>-21.1061959913334</v>
+        <v>-22.74532244314977</v>
       </c>
       <c r="F90">
-        <v>3.755052392449992</v>
+        <v>1.873248679959208</v>
       </c>
       <c r="G90">
-        <v>1.104512710326409</v>
+        <v>0.3705515220878293</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.713445245199448</v>
       </c>
       <c r="E91">
-        <v>-21.27922445469248</v>
+        <v>-24.48311075817124</v>
       </c>
       <c r="F91">
-        <v>4.222923463636437</v>
+        <v>1.470781495668581</v>
       </c>
       <c r="G91">
-        <v>1.471433714625991</v>
+        <v>-1.593773915820887</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.852433088367463</v>
       </c>
       <c r="E92">
-        <v>-22.31839149912863</v>
+        <v>-25.0244083132561</v>
       </c>
       <c r="F92">
-        <v>4.022074712028576</v>
+        <v>0.6319463182614311</v>
       </c>
       <c r="G92">
-        <v>2.095458306596453</v>
+        <v>0.762251959748857</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.037207347817778</v>
       </c>
       <c r="E93">
-        <v>-25.58417751381824</v>
+        <v>-27.6823870751102</v>
       </c>
       <c r="F93">
-        <v>3.144783987582724</v>
+        <v>0.811014362414254</v>
       </c>
       <c r="G93">
-        <v>0.9551309639578748</v>
+        <v>1.063379182000964</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.260653182347376</v>
       </c>
       <c r="E94">
-        <v>-27.33137599782765</v>
+        <v>-29.29658880598834</v>
       </c>
       <c r="F94">
-        <v>3.018423260001642</v>
+        <v>1.347482071622043</v>
       </c>
       <c r="G94">
-        <v>1.499258849883566</v>
+        <v>0.1900109211036752</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.518824308025338</v>
       </c>
       <c r="E95">
-        <v>-28.44443868112096</v>
+        <v>-29.98159295523261</v>
       </c>
       <c r="F95">
-        <v>2.320162570766643</v>
+        <v>0.3315600661622847</v>
       </c>
       <c r="G95">
-        <v>0.378520005200855</v>
+        <v>0.05670518387384225</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.810669021192693</v>
       </c>
       <c r="E96">
-        <v>-32.92508521055931</v>
+        <v>-35.27892260111026</v>
       </c>
       <c r="F96">
-        <v>2.195800480050845</v>
+        <v>0.08259278587266869</v>
       </c>
       <c r="G96">
-        <v>1.023791678442359</v>
+        <v>-0.9262255816456266</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.126933532407868</v>
       </c>
       <c r="E97">
-        <v>-32.97812949084816</v>
+        <v>-34.78228485668905</v>
       </c>
       <c r="F97">
-        <v>2.03618667936328</v>
+        <v>-0.1853955943143328</v>
       </c>
       <c r="G97">
-        <v>1.941296132469212</v>
+        <v>-1.111043407466519</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.465996992630238</v>
       </c>
       <c r="E98">
-        <v>-36.02433432937984</v>
+        <v>-39.02995951232879</v>
       </c>
       <c r="F98">
-        <v>1.602197412531747</v>
+        <v>-0.3857613156179854</v>
       </c>
       <c r="G98">
-        <v>0.4801703059841769</v>
+        <v>-0.5238089080739782</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.812360711847151</v>
       </c>
       <c r="E99">
-        <v>-38.07716631687794</v>
+        <v>-38.73980433299832</v>
       </c>
       <c r="F99">
-        <v>1.181313312150475</v>
+        <v>-1.090472439046569</v>
       </c>
       <c r="G99">
-        <v>0.488973046573099</v>
+        <v>-2.031133397559542</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.169069832819096</v>
       </c>
       <c r="E100">
-        <v>-40.31645369316786</v>
+        <v>-41.17117599127159</v>
       </c>
       <c r="F100">
-        <v>1.07152131585672</v>
+        <v>-1.326174598588464</v>
       </c>
       <c r="G100">
-        <v>1.611178462929707</v>
+        <v>-1.662752442677141</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.507946327188678</v>
       </c>
       <c r="E101">
-        <v>-42.00946445720149</v>
+        <v>-42.16926977645817</v>
       </c>
       <c r="F101">
-        <v>0.6868391489964777</v>
+        <v>-1.988201680184124</v>
       </c>
       <c r="G101">
-        <v>0.8747078811723599</v>
+        <v>-2.198726454939607</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.861338008385122</v>
       </c>
       <c r="E102">
-        <v>-44.26989754287023</v>
+        <v>-42.94657554716377</v>
       </c>
       <c r="F102">
-        <v>1.160845496899335</v>
+        <v>-1.626574312187892</v>
       </c>
       <c r="G102">
-        <v>0.5369726463469919</v>
+        <v>-2.871684220526036</v>
       </c>
     </row>
   </sheetData>
